--- a/data/trans_orig/P43E-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P43E-Estudios-trans_orig.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -525,25 +525,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha citología vaginal en 2012</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última citología vaginal en 2012 (tasa de respuesta: 98,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +547,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -563,17 +556,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -644,41 +626,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -701,13 +648,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -722,37 +662,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>78</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>87060</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>69499</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>106642</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +707,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70897</t>
+          <t>69499</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107087</t>
+          <t>106642</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,47 +722,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>87060</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>70897</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>107087</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>15,55%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -835,37 +740,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>565</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>601763</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>582181</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>619324</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +785,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>581736</t>
+          <t>582181</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>617926</t>
+          <t>619324</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,47 +800,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>565</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>601763</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>581736</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>617926</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>87,36%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>84,45%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>89,71%</t>
+          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -948,37 +818,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>643</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>688823</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>688823</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>688823</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1012,41 +882,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>688823</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>688823</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>688823</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1065,37 +900,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>253</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>281733</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>253294</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>313779</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +945,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>252070</t>
+          <t>253294</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>314468</t>
+          <t>313779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,47 +960,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>281733</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>252070</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>314468</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>23,22%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>20,78%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>25,92%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -1178,37 +978,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>862</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>931488</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>899442</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>959927</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1023,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>898753</t>
+          <t>899442</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>961151</t>
+          <t>959927</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,47 +1038,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>931488</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>898753</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>961151</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>76,78%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>74,08%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>79,22%</t>
+          <t>79,12%</t>
         </is>
       </c>
     </row>
@@ -1291,37 +1056,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1213221</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1355,41 +1120,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1115</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1213221</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1213221</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1213221</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1408,37 +1138,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>129</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>147677</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>128253</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>170404</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1183,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127793</t>
+          <t>128253</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>168352</t>
+          <t>170404</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,47 +1198,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>147677</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>127793</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>168352</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>42,93%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>37,15%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>48,94%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -1521,37 +1216,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>177</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>196333</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>173606</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>215757</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1261,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>175658</t>
+          <t>173606</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>216217</t>
+          <t>215757</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,47 +1276,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>196333</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>175658</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>216217</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>57,07%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>51,06%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>62,85%</t>
+          <t>62,72%</t>
         </is>
       </c>
     </row>
@@ -1634,37 +1294,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>306</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>344010</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>344010</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>344010</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1698,41 +1358,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>344010</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>344010</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>344010</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1751,37 +1376,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>460</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>516470</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>476533</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>565096</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1421,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>478630</t>
+          <t>476533</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>559000</t>
+          <t>565096</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,47 +1436,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>516470</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>478630</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>559000</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>22,99%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>21,31%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>24,89%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -1864,37 +1454,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1729584</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1680958</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1769521</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1499,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1687054</t>
+          <t>1680958</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1767424</t>
+          <t>1769521</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,47 +1514,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1604</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1729584</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1687054</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1767424</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>77,01%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>75,11%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>78,69%</t>
+          <t>78,78%</t>
         </is>
       </c>
     </row>
@@ -1977,37 +1532,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2246054</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2246054</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2246054</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2041,41 +1596,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>2064</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>2246054</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>2246054</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>2246054</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2089,13 +1609,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -2109,7 +1628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2128,25 +1647,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha citología vaginal en 2016</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última citología vaginal en 2016 (tasa de respuesta: 96,09%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +1669,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2166,17 +1678,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -2247,41 +1748,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -2304,13 +1770,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2325,37 +1784,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23807</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15094</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35364</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +1829,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14915</t>
+          <t>15094</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35755</t>
+          <t>35364</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,47 +1844,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>23807</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>14915</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>35755</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>7,52%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -2438,37 +1862,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>414</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>451595</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>440038</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>460308</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +1907,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>439647</t>
+          <t>440038</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>460487</t>
+          <t>460308</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,47 +1922,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>451595</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>439647</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>460487</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>94,99%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>92,48%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>96,86%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -2551,37 +1940,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>435</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>475402</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>475402</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>475402</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2615,41 +2004,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>475402</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>475402</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>475402</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2668,37 +2022,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>166</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>176081</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>152615</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>202691</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2067,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>153505</t>
+          <t>152615</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>202325</t>
+          <t>202691</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,47 +2082,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>176081</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>153505</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>202325</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>14,02%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>12,22%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>16,11%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -2781,37 +2100,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1079851</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1053241</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1103317</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2145,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1053607</t>
+          <t>1053241</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1102427</t>
+          <t>1103317</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,47 +2160,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1079851</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1053607</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1102427</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>85,98%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>83,89%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>87,78%</t>
+          <t>87,85%</t>
         </is>
       </c>
     </row>
@@ -2894,37 +2178,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1255932</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1255932</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1255932</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2958,41 +2242,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1205</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1255932</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1255932</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1255932</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3011,37 +2260,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>148730</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>128739</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>167989</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +2305,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127817</t>
+          <t>128739</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>168210</t>
+          <t>167989</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,47 +2320,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>148730</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>127817</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>168210</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>36,02%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>30,95%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>40,73%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -3124,37 +2338,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>253</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>264233</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>244974</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>284224</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +2383,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>244753</t>
+          <t>244974</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>285146</t>
+          <t>284224</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,47 +2398,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>264233</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>244753</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>285146</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>63,98%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>59,27%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>69,05%</t>
+          <t>68,83%</t>
         </is>
       </c>
     </row>
@@ -3237,37 +2416,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>391</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>412963</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>412963</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>412963</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3301,41 +2480,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>412963</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>412963</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>412963</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3354,37 +2498,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>325</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>348618</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>315608</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>382920</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +2543,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>311698</t>
+          <t>315608</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>383065</t>
+          <t>382920</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,45 +2558,10 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>17,86%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>348618</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>311698</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>383065</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>16,26%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>14,54%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>17,86%</t>
         </is>
@@ -3467,37 +2576,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1706</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1795679</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1761377</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1828689</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +2621,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1761232</t>
+          <t>1761377</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1832599</t>
+          <t>1828689</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3532,42 +2641,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1706</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1795679</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1761232</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1832599</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>83,74%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>82,14%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>85,46%</t>
+          <t>85,28%</t>
         </is>
       </c>
     </row>
@@ -3580,37 +2654,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2144297</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2144297</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2144297</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3644,41 +2718,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>2144297</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>2144297</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>2144297</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3692,13 +2731,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -3712,7 +2750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3731,25 +2769,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha citología vaginal en 2023</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última citología vaginal en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +2791,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3769,17 +2800,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -3850,41 +2870,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -3907,13 +2892,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3928,37 +2906,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17816</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24523</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +2951,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12227</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24576</t>
+          <t>24523</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,47 +2966,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>17816</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>12227</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>24576</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>8,6%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -4041,37 +2984,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>499</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267930</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>261223</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273381</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +3029,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261170</t>
+          <t>261223</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>273519</t>
+          <t>273381</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,47 +3044,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>267930</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>261170</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>273519</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>93,77%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>91,4%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>95,72%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -4154,37 +3062,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>532</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>285746</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>285746</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>285746</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4218,41 +3126,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>285746</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>285746</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>285746</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4271,37 +3144,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>271</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>175091</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>134069</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>202240</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +3189,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>132092</t>
+          <t>134069</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>205411</t>
+          <t>202240</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,47 +3204,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>175091</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>132092</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>205411</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>18,73%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>14,13%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>21,97%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -4384,37 +3222,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>759796</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>732647</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>800818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +3267,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>729476</t>
+          <t>732647</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>802795</t>
+          <t>800818</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,47 +3282,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>759796</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>729476</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>802795</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>81,27%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>78,03%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>85,87%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -4497,37 +3300,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>934887</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>934887</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>934887</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4561,41 +3364,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1336</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>934887</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>934887</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>934887</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4614,37 +3382,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>254</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>165765</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>150439</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>182905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +3427,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151066</t>
+          <t>150439</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>181739</t>
+          <t>182905</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,47 +3442,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>165765</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>151066</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>181739</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>47,81%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>43,57%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>52,42%</t>
+          <t>52,76%</t>
         </is>
       </c>
     </row>
@@ -4727,37 +3460,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>289</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>180917</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>163777</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>196243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +3505,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164943</t>
+          <t>163777</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>195616</t>
+          <t>196243</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,47 +3520,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>180917</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>164943</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>195616</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>52,19%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>47,58%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>56,43%</t>
+          <t>56,61%</t>
         </is>
       </c>
     </row>
@@ -4840,37 +3538,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>543</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>346682</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>346682</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>346682</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4904,41 +3602,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>346682</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>346682</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>346682</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4957,37 +3620,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>558</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>358672</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>297269</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>392207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +3665,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>303083</t>
+          <t>297269</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>396402</t>
+          <t>392207</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,47 +3680,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>558</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>358672</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>303083</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>396402</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>22,88%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>19,34%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>25,29%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -5070,37 +3698,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1208643</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1175108</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1270046</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +3743,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1170913</t>
+          <t>1175108</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1264232</t>
+          <t>1270046</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,47 +3758,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1853</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1208643</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1170913</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1264232</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>77,12%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>74,71%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>80,66%</t>
+          <t>81,03%</t>
         </is>
       </c>
     </row>
@@ -5183,37 +3776,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1567315</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1567315</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1567315</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5247,41 +3840,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>2411</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1567315</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1567315</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1567315</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5295,13 +3853,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_orig/P43E-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P43E-Estudios-trans_orig.xlsx
@@ -672,12 +672,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69499</t>
+          <t>69597</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106642</t>
+          <t>105566</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69499</t>
+          <t>69597</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106642</t>
+          <t>105566</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>582181</t>
+          <t>583257</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>619324</t>
+          <t>619226</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>582181</t>
+          <t>583257</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>619324</t>
+          <t>619226</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,9%</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>253294</t>
+          <t>252278</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>313779</t>
+          <t>313106</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>253294</t>
+          <t>252278</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313779</t>
+          <t>313106</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>899442</t>
+          <t>900115</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>959927</t>
+          <t>960943</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>899442</t>
+          <t>900115</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>959927</t>
+          <t>960943</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,21%</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128253</t>
+          <t>128582</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>170404</t>
+          <t>168737</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>128253</t>
+          <t>128582</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>170404</t>
+          <t>168737</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,05%</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>173606</t>
+          <t>175273</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>215757</t>
+          <t>215428</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>173606</t>
+          <t>175273</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>215757</t>
+          <t>215428</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,62%</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>476533</t>
+          <t>475469</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>565096</t>
+          <t>557737</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>476533</t>
+          <t>475469</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>565096</t>
+          <t>557737</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1680958</t>
+          <t>1688317</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1769521</t>
+          <t>1770585</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1680958</t>
+          <t>1688317</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1769521</t>
+          <t>1770585</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,83%</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15094</t>
+          <t>15182</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35364</t>
+          <t>35856</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15094</t>
+          <t>15182</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35364</t>
+          <t>35856</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>440038</t>
+          <t>439546</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>460308</t>
+          <t>460220</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>440038</t>
+          <t>439546</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>460308</t>
+          <t>460220</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>152615</t>
+          <t>152966</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>202691</t>
+          <t>202652</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>152615</t>
+          <t>152966</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>202691</t>
+          <t>202652</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1053241</t>
+          <t>1053280</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1103317</t>
+          <t>1102966</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1053241</t>
+          <t>1053280</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1103317</t>
+          <t>1102966</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,82%</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128739</t>
+          <t>129254</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>167989</t>
+          <t>170056</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>128739</t>
+          <t>129254</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>167989</t>
+          <t>170056</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>41,18%</t>
         </is>
       </c>
     </row>
@@ -2348,12 +2348,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>244974</t>
+          <t>242907</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>284224</t>
+          <t>283709</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>244974</t>
+          <t>242907</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>284224</t>
+          <t>283709</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,7%</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2508,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>315608</t>
+          <t>315699</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>382920</t>
+          <t>384152</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2543,12 +2543,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>315608</t>
+          <t>315699</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382920</t>
+          <t>384152</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1761377</t>
+          <t>1760145</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1828689</t>
+          <t>1828598</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1761377</t>
+          <t>1760145</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1828689</t>
+          <t>1828598</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17816</t>
+          <t>18819</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12365</t>
+          <t>13459</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24523</t>
+          <t>25525</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17816</t>
+          <t>18819</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12365</t>
+          <t>13459</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24523</t>
+          <t>25525</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>267930</t>
+          <t>284920</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>261223</t>
+          <t>278214</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>273381</t>
+          <t>290280</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>267930</t>
+          <t>284920</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261223</t>
+          <t>278214</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>273381</t>
+          <t>290280</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -3067,17 +3067,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>285746</t>
+          <t>303739</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>285746</t>
+          <t>303739</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>285746</t>
+          <t>303739</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3102,17 +3102,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>285746</t>
+          <t>303739</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>285746</t>
+          <t>303739</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>285746</t>
+          <t>303739</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>175091</t>
+          <t>194444</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>134069</t>
+          <t>175267</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>202240</t>
+          <t>216028</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>175091</t>
+          <t>194444</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134069</t>
+          <t>175267</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>202240</t>
+          <t>216028</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>759796</t>
+          <t>720482</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>732647</t>
+          <t>698898</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>800818</t>
+          <t>739659</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>759796</t>
+          <t>720482</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>732647</t>
+          <t>698898</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>800818</t>
+          <t>739659</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>80,84%</t>
         </is>
       </c>
     </row>
@@ -3305,17 +3305,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>934887</t>
+          <t>914926</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>934887</t>
+          <t>914926</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>934887</t>
+          <t>914926</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>934887</t>
+          <t>914926</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>934887</t>
+          <t>914926</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>934887</t>
+          <t>914926</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3387,32 +3387,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>165765</t>
+          <t>180579</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>150439</t>
+          <t>163538</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>182905</t>
+          <t>198622</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3422,32 +3422,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>165765</t>
+          <t>180579</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>150439</t>
+          <t>163538</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>182905</t>
+          <t>198622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>51,35%</t>
         </is>
       </c>
     </row>
@@ -3465,32 +3465,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>180917</t>
+          <t>206225</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>163777</t>
+          <t>188182</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>196243</t>
+          <t>223266</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3500,32 +3500,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>180917</t>
+          <t>206225</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>163777</t>
+          <t>188182</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>196243</t>
+          <t>223266</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -3543,17 +3543,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>346682</t>
+          <t>386804</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>346682</t>
+          <t>386804</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>346682</t>
+          <t>386804</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3578,17 +3578,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>346682</t>
+          <t>386804</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>346682</t>
+          <t>386804</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>346682</t>
+          <t>386804</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3625,32 +3625,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>358672</t>
+          <t>393843</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>297269</t>
+          <t>365038</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>392207</t>
+          <t>422719</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3660,32 +3660,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>358672</t>
+          <t>393843</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>297269</t>
+          <t>365038</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>392207</t>
+          <t>422719</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -3703,32 +3703,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1208643</t>
+          <t>1211626</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1175108</t>
+          <t>1182750</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1270046</t>
+          <t>1240431</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3738,32 +3738,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1208643</t>
+          <t>1211626</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1175108</t>
+          <t>1182750</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1270046</t>
+          <t>1240431</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>77,26%</t>
         </is>
       </c>
     </row>
@@ -3781,17 +3781,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1567315</t>
+          <t>1605469</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1567315</t>
+          <t>1605469</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1567315</t>
+          <t>1605469</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3816,17 +3816,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1567315</t>
+          <t>1605469</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1567315</t>
+          <t>1605469</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1567315</t>
+          <t>1605469</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
